--- a/data/trans_orig/P78A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P78A_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona sustentadora principal ha trabajado anteriormente en 2023</t>
+          <t>Población según si la persona sustentadora principal ha trabajado anteriormente en 2023 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75548</t>
+          <t>72790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>133541</t>
+          <t>132836</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52084</t>
+          <t>51378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88930</t>
+          <t>90585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>138714</t>
+          <t>139318</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>207699</t>
+          <t>206152</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163620</t>
+          <t>164325</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>221613</t>
+          <t>224371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135564</t>
+          <t>133909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>172410</t>
+          <t>173116</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>313957</t>
+          <t>315504</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>382942</t>
+          <t>382338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56754</t>
+          <t>58520</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74560</t>
+          <t>74603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>111045</t>
+          <t>112278</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>135357</t>
+          <t>135563</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>176494</t>
+          <t>176055</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205814</t>
+          <t>205412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>30241</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54759</t>
+          <t>53526</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>39231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68149</t>
+          <t>68588</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64466</t>
+          <t>64866</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74849</t>
+          <t>74828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>149427</t>
+          <t>150334</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166838</t>
+          <t>166281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>220065</t>
+          <t>220186</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>240250</t>
+          <t>239352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12609</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24288</t>
+          <t>24845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41699</t>
+          <t>40792</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27951</t>
+          <t>28849</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48136</t>
+          <t>48015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117606</t>
+          <t>117681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131118</t>
+          <t>131408</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180018</t>
+          <t>180180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>203398</t>
+          <t>203878</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>303251</t>
+          <t>303966</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>332088</t>
+          <t>330366</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19280</t>
+          <t>19205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61057</t>
+          <t>60577</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84437</t>
+          <t>84275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69253</t>
+          <t>70975</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98090</t>
+          <t>97375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>251029</t>
+          <t>250262</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>260004</t>
+          <t>260184</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>272490</t>
+          <t>272529</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>294589</t>
+          <t>294376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>528388</t>
+          <t>528213</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>551389</t>
+          <t>552185</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,98%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10551</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50734</t>
+          <t>50947</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72833</t>
+          <t>72794</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55514</t>
+          <t>54718</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78515</t>
+          <t>78690</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>344327</t>
+          <t>344280</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>350109</t>
+          <t>350166</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>544309</t>
+          <t>544316</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>581453</t>
+          <t>580051</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>899147</t>
+          <t>899417</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>928067</t>
+          <t>927076</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>580</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6419</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>10451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46193</t>
+          <t>46186</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>14173</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42102</t>
+          <t>41832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>277218</t>
+          <t>277186</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>341507</t>
+          <t>343418</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>364441</t>
+          <t>365156</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>624162</t>
+          <t>622291</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>646648</t>
+          <t>645634</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,52%</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59835</t>
+          <t>59120</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>82769</t>
+          <t>80858</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58789</t>
+          <t>59803</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>81275</t>
+          <t>83146</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1202066</t>
+          <t>1194297</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1290581</t>
+          <t>1289961</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1683269</t>
+          <t>1685046</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1878105</t>
+          <t>1862130</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2933330</t>
+          <t>2926382</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3136524</t>
+          <t>3123572</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>192867</t>
+          <t>193487</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>281382</t>
+          <t>289151</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>327875</t>
+          <t>343850</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>522711</t>
+          <t>520934</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>552904</t>
+          <t>565856</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>756098</t>
+          <t>763046</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P78A_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>101021</t>
+          <t>101597</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72790</t>
+          <t>76371</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>132836</t>
+          <t>128938</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>69428</t>
+          <t>79005</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51378</t>
+          <t>59957</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90585</t>
+          <t>100630</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>170450</t>
+          <t>180602</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139318</t>
+          <t>148589</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>206152</t>
+          <t>218461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>196140</t>
+          <t>189340</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>164325</t>
+          <t>161999</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>224371</t>
+          <t>214566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>155066</t>
+          <t>182996</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133909</t>
+          <t>161371</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>173116</t>
+          <t>202044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,85%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>351206</t>
+          <t>372336</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>315504</t>
+          <t>334477</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>382338</t>
+          <t>404349</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>297161</t>
+          <t>290937</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>297161</t>
+          <t>290937</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>297161</t>
+          <t>290937</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>224494</t>
+          <t>262001</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>224494</t>
+          <t>262001</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>224494</t>
+          <t>262001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>521656</t>
+          <t>552938</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>521656</t>
+          <t>552938</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>521656</t>
+          <t>552938</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68137</t>
+          <t>73445</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58520</t>
+          <t>62779</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74603</t>
+          <t>80646</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>124383</t>
+          <t>140349</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>112278</t>
+          <t>126225</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>135563</t>
+          <t>153584</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>192521</t>
+          <t>213794</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>176055</t>
+          <t>196676</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205412</t>
+          <t>228984</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>23578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41421</t>
+          <t>48243</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>30241</t>
+          <t>35008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53526</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>52122</t>
+          <t>61155</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39231</t>
+          <t>45965</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68588</t>
+          <t>78273</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78838</t>
+          <t>86357</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>78838</t>
+          <t>86357</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78838</t>
+          <t>86357</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>165804</t>
+          <t>188592</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>165804</t>
+          <t>188592</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>165804</t>
+          <t>188592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>244643</t>
+          <t>274949</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>244643</t>
+          <t>274949</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>244643</t>
+          <t>274949</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>71346</t>
+          <t>78940</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64866</t>
+          <t>72348</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74828</t>
+          <t>82462</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>159251</t>
+          <t>181062</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>150334</t>
+          <t>169671</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166281</t>
+          <t>190435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>230597</t>
+          <t>260003</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>220186</t>
+          <t>248721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>239352</t>
+          <t>271581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31875</t>
+          <t>43106</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>33733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40792</t>
+          <t>54497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>37604</t>
+          <t>49361</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28849</t>
+          <t>37783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48015</t>
+          <t>60643</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>19,6%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>77075</t>
+          <t>85196</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77075</t>
+          <t>85196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77075</t>
+          <t>85196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>191126</t>
+          <t>224168</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>191126</t>
+          <t>224168</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>191126</t>
+          <t>224168</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>268201</t>
+          <t>309364</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>268201</t>
+          <t>309364</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>268201</t>
+          <t>309364</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>126064</t>
+          <t>142011</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117681</t>
+          <t>133359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>131408</t>
+          <t>147573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>192158</t>
+          <t>212120</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>180180</t>
+          <t>199956</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>203878</t>
+          <t>224373</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>318223</t>
+          <t>354131</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>303966</t>
+          <t>339694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330366</t>
+          <t>367465</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19205</t>
+          <t>19661</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>72297</t>
+          <t>75845</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60577</t>
+          <t>63592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84275</t>
+          <t>88009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>83118</t>
+          <t>86854</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70975</t>
+          <t>73520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97375</t>
+          <t>101291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>22,97%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136886</t>
+          <t>153020</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136886</t>
+          <t>153020</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136886</t>
+          <t>153020</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>264455</t>
+          <t>287965</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>264455</t>
+          <t>287965</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>264455</t>
+          <t>287965</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>401341</t>
+          <t>440985</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>401341</t>
+          <t>440985</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>401341</t>
+          <t>440985</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>256994</t>
+          <t>273390</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>250262</t>
+          <t>266110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>260184</t>
+          <t>276991</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>283515</t>
+          <t>315675</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>272529</t>
+          <t>304236</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>294376</t>
+          <t>327458</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>540509</t>
+          <t>589065</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>528213</t>
+          <t>574608</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>552185</t>
+          <t>601115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>12998</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61808</t>
+          <t>68135</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50947</t>
+          <t>56352</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72794</t>
+          <t>79574</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>66394</t>
+          <t>73853</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54718</t>
+          <t>61803</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78690</t>
+          <t>88310</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>261580</t>
+          <t>279108</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>261580</t>
+          <t>279108</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>261580</t>
+          <t>279108</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>345323</t>
+          <t>383810</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>345323</t>
+          <t>383810</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>345323</t>
+          <t>383810</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>606903</t>
+          <t>662918</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>606903</t>
+          <t>662918</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>606903</t>
+          <t>662918</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>348279</t>
+          <t>384890</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>344280</t>
+          <t>380806</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>350166</t>
+          <t>386841</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>563263</t>
+          <t>389542</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>544316</t>
+          <t>381049</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>580051</t>
+          <t>396668</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>911543</t>
+          <t>774432</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>899417</t>
+          <t>765255</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>927076</t>
+          <t>782182</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>27239</t>
+          <t>29711</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10451</t>
+          <t>22585</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46186</t>
+          <t>38204</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>29706</t>
+          <t>32251</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14173</t>
+          <t>24501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41832</t>
+          <t>41428</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>350746</t>
+          <t>387430</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>350746</t>
+          <t>387430</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>350746</t>
+          <t>387430</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>590502</t>
+          <t>419253</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>590502</t>
+          <t>419253</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>590502</t>
+          <t>419253</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>941249</t>
+          <t>806683</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>941249</t>
+          <t>806683</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>941249</t>
+          <t>806683</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,27 +2783,27 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>280027</t>
+          <t>307203</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>277186</t>
+          <t>303865</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>281161</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>354816</t>
+          <t>387071</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>343418</t>
+          <t>373787</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>365156</t>
+          <t>399457</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>634843</t>
+          <t>694273</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>622291</t>
+          <t>679841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>645634</t>
+          <t>706865</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>69460</t>
+          <t>75816</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59120</t>
+          <t>63430</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>80858</t>
+          <t>89100</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>70594</t>
+          <t>76995</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>64403</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83146</t>
+          <t>91427</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281161</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281161</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281161</t>
+          <t>308382</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424276</t>
+          <t>462887</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424276</t>
+          <t>462887</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424276</t>
+          <t>462887</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>705437</t>
+          <t>771268</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>705437</t>
+          <t>771268</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>705437</t>
+          <t>771268</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1251869</t>
+          <t>1361478</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1194297</t>
+          <t>1317882</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1289961</t>
+          <t>1400476</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1746814</t>
+          <t>1704824</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1685046</t>
+          <t>1656945</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1862130</t>
+          <t>1741603</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2998684</t>
+          <t>3066302</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2926382</t>
+          <t>3006077</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3123572</t>
+          <t>3123037</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>231579</t>
+          <t>228952</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>193487</t>
+          <t>189954</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>289151</t>
+          <t>272548</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>459166</t>
+          <t>523852</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>343850</t>
+          <t>487073</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>520934</t>
+          <t>571731</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>690744</t>
+          <t>752804</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>565856</t>
+          <t>696069</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>763046</t>
+          <t>813029</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1483448</t>
+          <t>1590430</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1483448</t>
+          <t>1590430</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1483448</t>
+          <t>1590430</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2205980</t>
+          <t>2228676</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2205980</t>
+          <t>2228676</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2205980</t>
+          <t>2228676</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3689428</t>
+          <t>3819106</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3689428</t>
+          <t>3819106</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3689428</t>
+          <t>3819106</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
